--- a/Libraries/Pandas/student_records_20.xlsx
+++ b/Libraries/Pandas/student_records_20.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data Analytics 604 batch ws\Libraries\Pandas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8976"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
   <si>
     <t>student_id</t>
   </si>
@@ -119,13 +124,16 @@
   </si>
   <si>
     <t>Testing</t>
+  </si>
+  <si>
+    <t>Yashasvi Dalvi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +196,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -234,7 +250,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,9 +282,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -300,6 +317,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -475,11 +493,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -509,9 +535,6 @@
       <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
       <c r="E2">
         <v>40000</v>
       </c>
@@ -519,7 +542,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -539,7 +562,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -559,27 +582,21 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="E5">
-        <v>30000</v>
-      </c>
       <c r="F5">
         <v>20000</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -599,303 +616,365 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
+        <v>1005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>25000</v>
+      </c>
+      <c r="F7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>1006</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>40000</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>35000</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>1007</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>50000</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>1008</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>30000</v>
-      </c>
-      <c r="F9">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
       </c>
       <c r="E10">
         <v>30000</v>
       </c>
       <c r="F10">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1008</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>30000</v>
+      </c>
+      <c r="F11">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1009</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>30000</v>
+      </c>
+      <c r="F12">
         <v>22000</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>1010</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>34</v>
       </c>
-      <c r="E11">
+      <c r="E13">
         <v>25000</v>
       </c>
-      <c r="F11">
+      <c r="F13">
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>1011</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>30</v>
       </c>
-      <c r="E12">
+      <c r="E14">
         <v>40000</v>
       </c>
-      <c r="F12">
+      <c r="F14">
         <v>30000</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>1012</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>31</v>
       </c>
-      <c r="E13">
+      <c r="E15">
         <v>50000</v>
       </c>
-      <c r="F13">
+      <c r="F15">
         <v>50000</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>1013</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>18</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>26</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D16" t="s">
         <v>32</v>
-      </c>
-      <c r="E14">
-        <v>30000</v>
-      </c>
-      <c r="F14">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>1014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15">
-        <v>30000</v>
-      </c>
-      <c r="F15">
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>1015</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16">
-        <v>25000</v>
       </c>
       <c r="F16">
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
+        <v>1014</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>30000</v>
+      </c>
+      <c r="F17">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1015</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18">
+        <v>25000</v>
+      </c>
+      <c r="F18">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>1016</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>21</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>30</v>
       </c>
-      <c r="E17">
+      <c r="E19">
         <v>40000</v>
       </c>
-      <c r="F17">
+      <c r="F19">
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1016</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>40000</v>
+      </c>
+      <c r="F20">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>1017</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C21" t="s">
         <v>26</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D21" t="s">
         <v>31</v>
       </c>
-      <c r="E18">
+      <c r="E21">
         <v>50000</v>
       </c>
-      <c r="F18">
+      <c r="F21">
         <v>35000</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>1018</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C22" t="s">
         <v>27</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D22" t="s">
         <v>32</v>
       </c>
-      <c r="E19">
+      <c r="E22">
         <v>30000</v>
       </c>
-      <c r="F19">
+      <c r="F22">
         <v>30000</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>1019</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B23" t="s">
         <v>24</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D23" t="s">
         <v>33</v>
       </c>
-      <c r="E20">
+      <c r="E23">
         <v>30000</v>
       </c>
-      <c r="F20">
+      <c r="F23">
         <v>18000</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>1020</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D24" t="s">
         <v>34</v>
       </c>
-      <c r="E21">
-        <v>25000</v>
-      </c>
-      <c r="F21">
+      <c r="F24">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1021</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25">
+        <v>40000</v>
+      </c>
+      <c r="F25">
         <v>22000</v>
       </c>
     </row>
